--- a/Check.xlsx
+++ b/Check.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="106">
   <si>
     <t>Группа проверок/модуль</t>
   </si>
@@ -25,6 +25,9 @@
     <t>Результат</t>
   </si>
   <si>
+    <t>Сортировка  по степени автоматизации</t>
+  </si>
+  <si>
     <t>Авторизация</t>
   </si>
   <si>
@@ -35,6 +38,9 @@
   </si>
   <si>
     <t>Passed</t>
+  </si>
+  <si>
+    <t>Auto</t>
   </si>
   <si>
     <t>Успешное завершение пользовательской сессии (logout)</t>
@@ -266,6 +272,9 @@
     <t>Корректное отображение интерфейса на устройствах с различными разрешениями экрана</t>
   </si>
   <si>
+    <t>Manual</t>
+  </si>
+  <si>
     <t>Поддержка темной/светлой темы</t>
   </si>
   <si>
@@ -346,7 +355,7 @@
     </font>
     <font/>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -375,6 +384,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEAD1DC"/>
         <bgColor rgb="FFEAD1DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -428,7 +443,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -444,7 +459,7 @@
     <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -459,6 +474,9 @@
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -702,7 +720,9 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5"/>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
@@ -727,18 +747,20 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
@@ -764,15 +786,17 @@
     <row r="3">
       <c r="A3" s="9"/>
       <c r="B3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -798,15 +822,17 @@
     <row r="4">
       <c r="A4" s="9"/>
       <c r="B4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
@@ -832,15 +858,17 @@
     <row r="5">
       <c r="A5" s="9"/>
       <c r="B5" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -866,15 +894,17 @@
     <row r="6">
       <c r="A6" s="9"/>
       <c r="B6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="6"/>
+      <c r="E6" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
@@ -900,15 +930,17 @@
     <row r="7">
       <c r="A7" s="9"/>
       <c r="B7" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
@@ -934,15 +966,17 @@
     <row r="8">
       <c r="A8" s="9"/>
       <c r="B8" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
@@ -968,15 +1002,17 @@
     <row r="9">
       <c r="A9" s="10"/>
       <c r="B9" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
@@ -1001,18 +1037,20 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
@@ -1038,15 +1076,17 @@
     <row r="11">
       <c r="A11" s="9"/>
       <c r="B11" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="6"/>
@@ -1072,15 +1112,17 @@
     <row r="12">
       <c r="A12" s="10"/>
       <c r="B12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>18</v>
-      </c>
       <c r="D12" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
@@ -1105,18 +1147,20 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -1142,15 +1186,17 @@
     <row r="14">
       <c r="A14" s="9"/>
       <c r="B14" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
@@ -1176,15 +1222,17 @@
     <row r="15">
       <c r="A15" s="10"/>
       <c r="B15" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -1209,18 +1257,20 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -1246,15 +1296,17 @@
     <row r="17">
       <c r="A17" s="9"/>
       <c r="B17" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -1280,15 +1332,17 @@
     <row r="18">
       <c r="A18" s="9"/>
       <c r="B18" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -1314,15 +1368,17 @@
     <row r="19">
       <c r="A19" s="9"/>
       <c r="B19" s="8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
@@ -1348,15 +1404,17 @@
     <row r="20">
       <c r="A20" s="9"/>
       <c r="B20" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
       <c r="H20" s="6"/>
@@ -1382,15 +1440,17 @@
     <row r="21">
       <c r="A21" s="9"/>
       <c r="B21" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -1416,15 +1476,17 @@
     <row r="22">
       <c r="A22" s="10"/>
       <c r="B22" s="8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
@@ -1449,18 +1511,20 @@
     </row>
     <row r="23">
       <c r="A23" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
@@ -1486,15 +1550,17 @@
     <row r="24">
       <c r="A24" s="9"/>
       <c r="B24" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F24" s="6"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
@@ -1520,15 +1586,17 @@
     <row r="25">
       <c r="A25" s="9"/>
       <c r="B25" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -1554,15 +1622,17 @@
     <row r="26">
       <c r="A26" s="9"/>
       <c r="B26" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
@@ -1588,15 +1658,17 @@
     <row r="27">
       <c r="A27" s="9"/>
       <c r="B27" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
@@ -1622,15 +1694,17 @@
     <row r="28">
       <c r="A28" s="9"/>
       <c r="B28" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
@@ -1656,15 +1730,17 @@
     <row r="29">
       <c r="A29" s="9"/>
       <c r="B29" s="8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
@@ -1690,15 +1766,17 @@
     <row r="30">
       <c r="A30" s="9"/>
       <c r="B30" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="6"/>
@@ -1724,15 +1802,17 @@
     <row r="31">
       <c r="A31" s="9"/>
       <c r="B31" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
@@ -1758,15 +1838,17 @@
     <row r="32">
       <c r="A32" s="9"/>
       <c r="B32" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
@@ -1792,15 +1874,17 @@
     <row r="33">
       <c r="A33" s="9"/>
       <c r="B33" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E33" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
@@ -1826,15 +1910,17 @@
     <row r="34">
       <c r="A34" s="9"/>
       <c r="B34" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E34" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
@@ -1860,15 +1946,17 @@
     <row r="35">
       <c r="A35" s="9"/>
       <c r="B35" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E35" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
@@ -1894,15 +1982,17 @@
     <row r="36">
       <c r="A36" s="9"/>
       <c r="B36" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
@@ -1928,15 +2018,17 @@
     <row r="37">
       <c r="A37" s="9"/>
       <c r="B37" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E37" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
@@ -1962,15 +2054,17 @@
     <row r="38">
       <c r="A38" s="9"/>
       <c r="B38" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
@@ -1996,15 +2090,17 @@
     <row r="39">
       <c r="A39" s="9"/>
       <c r="B39" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E39" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
@@ -2030,15 +2126,17 @@
     <row r="40">
       <c r="A40" s="9"/>
       <c r="B40" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
@@ -2064,15 +2162,17 @@
     <row r="41">
       <c r="A41" s="9"/>
       <c r="B41" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E41" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
@@ -2098,15 +2198,17 @@
     <row r="42">
       <c r="A42" s="9"/>
       <c r="B42" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E42" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
@@ -2132,15 +2234,17 @@
     <row r="43">
       <c r="A43" s="9"/>
       <c r="B43" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E43" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
@@ -2166,15 +2270,17 @@
     <row r="44">
       <c r="A44" s="9"/>
       <c r="B44" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
@@ -2200,15 +2306,17 @@
     <row r="45">
       <c r="A45" s="9"/>
       <c r="B45" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E45" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
@@ -2234,15 +2342,17 @@
     <row r="46">
       <c r="A46" s="9"/>
       <c r="B46" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
@@ -2268,15 +2378,17 @@
     <row r="47">
       <c r="A47" s="9"/>
       <c r="B47" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E47" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
@@ -2302,15 +2414,17 @@
     <row r="48">
       <c r="A48" s="10"/>
       <c r="B48" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
@@ -2335,18 +2449,20 @@
     </row>
     <row r="49">
       <c r="A49" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E49" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F49" s="6"/>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
@@ -2372,15 +2488,17 @@
     <row r="50">
       <c r="A50" s="9"/>
       <c r="B50" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E50" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F50" s="6"/>
       <c r="G50" s="6"/>
       <c r="H50" s="6"/>
@@ -2406,15 +2524,17 @@
     <row r="51">
       <c r="A51" s="9"/>
       <c r="B51" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E51" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
       <c r="H51" s="6"/>
@@ -2440,15 +2560,17 @@
     <row r="52">
       <c r="A52" s="9"/>
       <c r="B52" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E52" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F52" s="6"/>
       <c r="G52" s="6"/>
       <c r="H52" s="6"/>
@@ -2474,15 +2596,17 @@
     <row r="53">
       <c r="A53" s="9"/>
       <c r="B53" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E53" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
       <c r="H53" s="6"/>
@@ -2508,15 +2632,17 @@
     <row r="54">
       <c r="A54" s="9"/>
       <c r="B54" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E54" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
       <c r="H54" s="6"/>
@@ -2542,15 +2668,17 @@
     <row r="55">
       <c r="A55" s="9"/>
       <c r="B55" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E55" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
@@ -2576,15 +2704,17 @@
     <row r="56">
       <c r="A56" s="9"/>
       <c r="B56" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E56" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
       <c r="H56" s="6"/>
@@ -2610,15 +2740,17 @@
     <row r="57">
       <c r="A57" s="9"/>
       <c r="B57" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E57" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
       <c r="H57" s="6"/>
@@ -2644,15 +2776,17 @@
     <row r="58">
       <c r="A58" s="9"/>
       <c r="B58" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
       <c r="H58" s="6"/>
@@ -2678,15 +2812,17 @@
     <row r="59">
       <c r="A59" s="9"/>
       <c r="B59" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E59" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F59" s="6"/>
       <c r="G59" s="6"/>
       <c r="H59" s="6"/>
@@ -2712,15 +2848,17 @@
     <row r="60">
       <c r="A60" s="9"/>
       <c r="B60" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E60" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F60" s="6"/>
       <c r="G60" s="6"/>
       <c r="H60" s="6"/>
@@ -2746,15 +2884,17 @@
     <row r="61">
       <c r="A61" s="9"/>
       <c r="B61" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E61" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F61" s="6"/>
       <c r="G61" s="6"/>
       <c r="H61" s="6"/>
@@ -2780,15 +2920,17 @@
     <row r="62">
       <c r="A62" s="9"/>
       <c r="B62" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E62" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F62" s="6"/>
       <c r="G62" s="6"/>
       <c r="H62" s="6"/>
@@ -2814,15 +2956,17 @@
     <row r="63">
       <c r="A63" s="9"/>
       <c r="B63" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E63" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F63" s="6"/>
       <c r="G63" s="6"/>
       <c r="H63" s="6"/>
@@ -2848,15 +2992,17 @@
     <row r="64">
       <c r="A64" s="9"/>
       <c r="B64" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E64" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F64" s="6"/>
       <c r="G64" s="6"/>
       <c r="H64" s="6"/>
@@ -2882,15 +3028,17 @@
     <row r="65">
       <c r="A65" s="10"/>
       <c r="B65" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E65" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F65" s="6"/>
       <c r="G65" s="6"/>
       <c r="H65" s="6"/>
@@ -2915,18 +3063,20 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E66" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F66" s="6"/>
       <c r="G66" s="6"/>
       <c r="H66" s="6"/>
@@ -2952,15 +3102,17 @@
     <row r="67">
       <c r="A67" s="9"/>
       <c r="B67" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E67" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F67" s="6"/>
       <c r="G67" s="6"/>
       <c r="H67" s="6"/>
@@ -2986,15 +3138,17 @@
     <row r="68">
       <c r="A68" s="9"/>
       <c r="B68" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E68" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F68" s="6"/>
       <c r="G68" s="6"/>
       <c r="H68" s="6"/>
@@ -3020,15 +3174,17 @@
     <row r="69">
       <c r="A69" s="9"/>
       <c r="B69" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E69" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F69" s="6"/>
       <c r="G69" s="6"/>
       <c r="H69" s="6"/>
@@ -3054,15 +3210,17 @@
     <row r="70">
       <c r="A70" s="9"/>
       <c r="B70" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E70" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F70" s="6"/>
       <c r="G70" s="6"/>
       <c r="H70" s="6"/>
@@ -3088,15 +3246,17 @@
     <row r="71">
       <c r="A71" s="9"/>
       <c r="B71" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E71" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F71" s="6"/>
       <c r="G71" s="6"/>
       <c r="H71" s="6"/>
@@ -3122,15 +3282,17 @@
     <row r="72">
       <c r="A72" s="9"/>
       <c r="B72" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E72" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F72" s="6"/>
       <c r="G72" s="6"/>
       <c r="H72" s="6"/>
@@ -3156,15 +3318,17 @@
     <row r="73">
       <c r="A73" s="9"/>
       <c r="B73" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E73" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F73" s="6"/>
       <c r="G73" s="6"/>
       <c r="H73" s="6"/>
@@ -3190,15 +3354,17 @@
     <row r="74">
       <c r="A74" s="9"/>
       <c r="B74" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E74" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F74" s="6"/>
       <c r="G74" s="6"/>
       <c r="H74" s="6"/>
@@ -3224,15 +3390,17 @@
     <row r="75">
       <c r="A75" s="9"/>
       <c r="B75" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E75" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
       <c r="H75" s="6"/>
@@ -3258,15 +3426,17 @@
     <row r="76">
       <c r="A76" s="9"/>
       <c r="B76" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E76" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
       <c r="H76" s="6"/>
@@ -3292,15 +3462,17 @@
     <row r="77">
       <c r="A77" s="9"/>
       <c r="B77" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E77" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F77" s="6"/>
       <c r="G77" s="6"/>
       <c r="H77" s="6"/>
@@ -3326,15 +3498,17 @@
     <row r="78">
       <c r="A78" s="9"/>
       <c r="B78" s="8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E78" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F78" s="6"/>
       <c r="G78" s="6"/>
       <c r="H78" s="6"/>
@@ -3360,15 +3534,17 @@
     <row r="79">
       <c r="A79" s="9"/>
       <c r="B79" s="8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E79" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F79" s="6"/>
       <c r="G79" s="6"/>
       <c r="H79" s="6"/>
@@ -3394,15 +3570,17 @@
     <row r="80">
       <c r="A80" s="9"/>
       <c r="B80" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E80" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
       <c r="H80" s="6"/>
@@ -3428,15 +3606,17 @@
     <row r="81">
       <c r="A81" s="9"/>
       <c r="B81" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E81" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
       <c r="H81" s="6"/>
@@ -3462,15 +3642,17 @@
     <row r="82">
       <c r="A82" s="9"/>
       <c r="B82" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E82" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F82" s="6"/>
       <c r="G82" s="6"/>
       <c r="H82" s="6"/>
@@ -3496,15 +3678,17 @@
     <row r="83">
       <c r="A83" s="9"/>
       <c r="B83" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E83" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F83" s="6"/>
       <c r="G83" s="6"/>
       <c r="H83" s="6"/>
@@ -3530,15 +3714,17 @@
     <row r="84">
       <c r="A84" s="9"/>
       <c r="B84" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E84" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F84" s="6"/>
       <c r="G84" s="6"/>
       <c r="H84" s="6"/>
@@ -3564,15 +3750,17 @@
     <row r="85">
       <c r="A85" s="10"/>
       <c r="B85" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E85" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="F85" s="6"/>
       <c r="G85" s="6"/>
       <c r="H85" s="6"/>
@@ -3597,18 +3785,20 @@
     </row>
     <row r="86">
       <c r="A86" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="B86" s="12" t="s">
+        <v>85</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E86" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="F86" s="6"/>
       <c r="G86" s="6"/>
       <c r="H86" s="6"/>
@@ -3633,16 +3823,18 @@
     </row>
     <row r="87">
       <c r="A87" s="9"/>
-      <c r="B87" s="5" t="s">
-        <v>84</v>
+      <c r="B87" s="12" t="s">
+        <v>87</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E87" s="6"/>
+        <v>12</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
       <c r="H87" s="6"/>
@@ -3667,16 +3859,18 @@
     </row>
     <row r="88">
       <c r="A88" s="10"/>
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C88" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D88" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E88" s="6"/>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
       <c r="H88" s="6"/>
@@ -3701,18 +3895,20 @@
     </row>
     <row r="89">
       <c r="A89" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
+      </c>
+      <c r="B89" s="12" t="s">
+        <v>91</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E89" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="F89" s="6"/>
       <c r="G89" s="6"/>
       <c r="H89" s="6"/>
@@ -3737,16 +3933,18 @@
     </row>
     <row r="90">
       <c r="A90" s="9"/>
-      <c r="B90" s="12" t="s">
-        <v>89</v>
+      <c r="B90" s="13" t="s">
+        <v>92</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E90" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="F90" s="6"/>
       <c r="G90" s="6"/>
       <c r="H90" s="6"/>
@@ -3771,16 +3969,18 @@
     </row>
     <row r="91">
       <c r="A91" s="9"/>
-      <c r="B91" s="12" t="s">
-        <v>90</v>
+      <c r="B91" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E91" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="F91" s="6"/>
       <c r="G91" s="6"/>
       <c r="H91" s="6"/>
@@ -3805,16 +4005,18 @@
     </row>
     <row r="92">
       <c r="A92" s="9"/>
-      <c r="B92" s="12" t="s">
-        <v>91</v>
+      <c r="B92" s="13" t="s">
+        <v>94</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E92" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
       <c r="H92" s="6"/>
@@ -3839,16 +4041,18 @@
     </row>
     <row r="93">
       <c r="A93" s="10"/>
-      <c r="B93" s="12" t="s">
-        <v>92</v>
+      <c r="B93" s="13" t="s">
+        <v>95</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E93" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E93" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
       <c r="H93" s="6"/>
@@ -3873,18 +4077,20 @@
     </row>
     <row r="94">
       <c r="A94" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>97</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E94" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
       <c r="H94" s="6"/>
@@ -3909,16 +4115,18 @@
     </row>
     <row r="95">
       <c r="A95" s="9"/>
-      <c r="B95" s="12" t="s">
-        <v>95</v>
+      <c r="B95" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E95" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="F95" s="6"/>
       <c r="G95" s="6"/>
       <c r="H95" s="6"/>
@@ -3943,16 +4151,18 @@
     </row>
     <row r="96">
       <c r="A96" s="9"/>
-      <c r="B96" s="12" t="s">
-        <v>96</v>
+      <c r="B96" s="13" t="s">
+        <v>99</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E96" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
       <c r="H96" s="6"/>
@@ -3977,16 +4187,18 @@
     </row>
     <row r="97">
       <c r="A97" s="9"/>
-      <c r="B97" s="12" t="s">
-        <v>97</v>
+      <c r="B97" s="13" t="s">
+        <v>100</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E97" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
       <c r="H97" s="6"/>
@@ -4011,16 +4223,18 @@
     </row>
     <row r="98">
       <c r="A98" s="10"/>
-      <c r="B98" s="12" t="s">
-        <v>98</v>
+      <c r="B98" s="13" t="s">
+        <v>101</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E98" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
       <c r="H98" s="6"/>
@@ -4045,18 +4259,20 @@
     </row>
     <row r="99">
       <c r="A99" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
+      </c>
+      <c r="B99" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E99" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="F99" s="6"/>
       <c r="G99" s="6"/>
       <c r="H99" s="6"/>
@@ -4081,16 +4297,18 @@
     </row>
     <row r="100">
       <c r="A100" s="9"/>
-      <c r="B100" s="12" t="s">
-        <v>101</v>
+      <c r="B100" s="13" t="s">
+        <v>104</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E100" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="F100" s="6"/>
       <c r="G100" s="6"/>
       <c r="H100" s="6"/>
@@ -4116,15 +4334,17 @@
     <row r="101">
       <c r="A101" s="10"/>
       <c r="B101" s="8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E101" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="F101" s="6"/>
       <c r="G101" s="6"/>
       <c r="H101" s="6"/>
@@ -29701,6 +29921,9 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2:C101">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E101">
+      <formula1>"Manual,Auto"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D101">
       <formula1>"Failed,Passed"</formula1>
     </dataValidation>
